--- a/artfynd/A 35406-2024 artfynd.xlsx
+++ b/artfynd/A 35406-2024 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119286719</v>
+        <v>119286713</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tarsjön, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581352</v>
+        <v>581408</v>
       </c>
       <c r="R2" t="n">
-        <v>7059961</v>
+        <v>7060023</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,12 +775,7 @@
         <v>119286716</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119286714</v>
+        <v>119286718</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581408</v>
+        <v>581354</v>
       </c>
       <c r="R4" t="n">
-        <v>7060023</v>
+        <v>7059966</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119286723</v>
+        <v>119286715</v>
       </c>
       <c r="B5" t="n">
-        <v>78262</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581334</v>
+        <v>581449</v>
       </c>
       <c r="R5" t="n">
-        <v>7059920</v>
+        <v>7060005</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119286713</v>
+        <v>119286722</v>
       </c>
       <c r="B6" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581408</v>
+        <v>581341</v>
       </c>
       <c r="R6" t="n">
-        <v>7060023</v>
+        <v>7059941</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119286722</v>
+        <v>119286719</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,34 +1171,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tarsjön, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581341</v>
+        <v>581352</v>
       </c>
       <c r="R7" t="n">
-        <v>7059941</v>
+        <v>7059961</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,15 +1261,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119286718</v>
+        <v>119286720</v>
       </c>
       <c r="B8" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,21 +1272,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581354</v>
+        <v>581339</v>
       </c>
       <c r="R8" t="n">
-        <v>7059966</v>
+        <v>7059946</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,15 +1358,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119286715</v>
+        <v>119286714</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,21 +1369,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1393,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581449</v>
+        <v>581408</v>
       </c>
       <c r="R9" t="n">
-        <v>7060005</v>
+        <v>7060023</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,37 +1455,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119286720</v>
+        <v>119286723</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581339</v>
+        <v>581334</v>
       </c>
       <c r="R10" t="n">
-        <v>7059946</v>
+        <v>7059920</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 35406-2024 artfynd.xlsx
+++ b/artfynd/A 35406-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286713</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286716</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286718</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286715</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286722</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286719</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286720</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286714</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,8 +1594,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286723</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>